--- a/lessons/gallery/excels/remarks_minimal.xlsx
+++ b/lessons/gallery/excels/remarks_minimal.xlsx
@@ -383,7 +383,7 @@
     </comment>
     <comment ref="J41" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +/ (00:00:00), +123456 (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +&gt; (00:00:00), +Boolean (00:00:00), +JS (00:00:00), +MyBoolean (00:00:00), +a (00:00:00), +appendchild (00:00:00), +are (00:00:00), +are (00:00:00), +automatically (00:00:00), +characters (00:00:00), +contain (00:00:00), +container (00:00:00), +cript (00:00:00), +document (00:00:00), +for (00:00:00), +getElementById (00:00:00), +global (00:00:00), +ids (00:00:00), +invalid (00:00:00), +like (00:00:00), +my (00:00:00), +mynumber (00:00:00), +mystring (00:00:00), +names (00:00:00), +names (00:00:00), +need (00:00:00), +no (00:00:00), +numbers (00:00:00), +opposite (00:00:00), +oppositeboolean (00:00:00), +or (00:00:00), +spaces (00:00:00), +special (00:00:00), +start (00:00:00), +string (00:00:00), +that (00:00:00), +valid (00:00:00), +variables (00:00:00), +with (00:00:00), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+        <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +/ (00:00:00), +123456 (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +&gt; (00:00:00), +Boolean (00:00:00), +JS (00:00:00), +MyBoolean (00:00:00), +a (00:00:00), +appendchild (00:00:00), +are (00:00:00), +are (00:00:00), +automatically (00:00:00), +characters (00:00:00), +contain (00:00:00), +container (00:00:00), +cript (00:00:00), +document (00:00:00), +for (00:00:00), +getElementById (00:00:00), +global (00:00:00), +ids (00:00:00), +invalid (00:00:00), +like (00:00:00), +my (00:00:00), +mynumber (00:00:00), +mystring (00:00:00), +names (00:00:00), +names (00:00:00), +need (00:00:00), +no (00:00:00), +numbers (00:00:00), +opposite (00:00:00), +oppositeboolean (00:00:00), +or (00:00:00), +spaces (00:00:00), +special (00:00:00), +start (00:00:00), +string (00:00:00), +that (00:00:00), +valid (00:00:00), +variables (00:00:00), +with (00:00:00), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Academy (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="M41" authorId="0" shapeId="0">
@@ -393,7 +393,7 @@
     </comment>
     <comment ref="O41" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Academy (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +/ (00:00:00), +123456 (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +&gt; (00:00:00), +Boolean (00:00:00), +JS (00:00:00), +MyBoolean (00:00:00), +a (00:00:00), +appendchild (00:00:00), +are (00:00:00), +are (00:00:00), +automatically (00:00:00), +characters (00:00:00), +contain (00:00:00), +container (00:00:00), +cript (00:00:00), +document (00:00:00), +for (00:00:00), +getElementById (00:00:00), +global (00:00:00), +ids (00:00:00), +invalid (00:00:00), +like (00:00:00), +my (00:00:00), +mynumber (00:00:00), +mystring (00:00:00), +names (00:00:00), +names (00:00:00), +need (00:00:00), +no (00:00:00), +numbers (00:00:00), +opposite (00:00:00), +oppositeboolean (00:00:00), +or (00:00:00), +spaces (00:00:00), +special (00:00:00), +start (00:00:00), +string (00:00:00), +that (00:00:00), +valid (00:00:00), +variables (00:00:00), +with (00:00:00), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+          <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +/ (00:00:00), +123456 (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +&gt; (00:00:00), +Boolean (00:00:00), +JS (00:00:00), +MyBoolean (00:00:00), +a (00:00:00), +appendchild (00:00:00), +are (00:00:00), +are (00:00:00), +automatically (00:00:00), +characters (00:00:00), +contain (00:00:00), +container (00:00:00), +cript (00:00:00), +document (00:00:00), +for (00:00:00), +getElementById (00:00:00), +global (00:00:00), +ids (00:00:00), +invalid (00:00:00), +like (00:00:00), +my (00:00:00), +mynumber (00:00:00), +mystring (00:00:00), +names (00:00:00), +names (00:00:00), +need (00:00:00), +no (00:00:00), +numbers (00:00:00), +opposite (00:00:00), +oppositeboolean (00:00:00), +or (00:00:00), +spaces (00:00:00), +special (00:00:00), +start (00:00:00), +string (00:00:00), +that (00:00:00), +valid (00:00:00), +variables (00:00:00), +with (00:00:00), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Academy (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Academy (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
